--- a/docs/Files/Mid-format_model/ODYM_T6_RecycledProductsYieldLoss_V1.0.xlsx
+++ b/docs/Files/Mid-format_model/ODYM_T6_RecycledProductsYieldLoss_V1.0.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F6636D-387D-427B-A2E2-DD003B6F0F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEDCD403-4ADD-4471-9628-517392378B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="3" r:id="rId1"/>
@@ -339,12 +339,6 @@
     <t>Share of input material lost as fabrication scrap</t>
   </si>
   <si>
-    <t>EV LIB</t>
-  </si>
-  <si>
-    <t>other EV LIB products</t>
-  </si>
-  <si>
     <t>LIB</t>
   </si>
   <si>
@@ -364,6 +358,12 @@
   </si>
   <si>
     <t>ODYM_Classifications_MF</t>
+  </si>
+  <si>
+    <t>MF LIB</t>
+  </si>
+  <si>
+    <t>other MF LIB products</t>
   </si>
 </sst>
 </file>
@@ -820,7 +820,7 @@
         <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>16</v>
@@ -890,7 +890,7 @@
         <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>16</v>
@@ -904,7 +904,7 @@
         <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>16</v>
@@ -988,7 +988,7 @@
         <v>36</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>16</v>
@@ -1216,13 +1216,13 @@
         <v>56</v>
       </c>
       <c r="B2" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" t="s">
         <v>102</v>
       </c>
-      <c r="C2" t="s">
-        <v>104</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1245,13 +1245,13 @@
         <v>56</v>
       </c>
       <c r="B3" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" t="s">
         <v>103</v>
       </c>
-      <c r="C3" t="s">
-        <v>105</v>
-      </c>
       <c r="D3" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E3">
         <v>0</v>
